--- a/十全特好_7-9月FB貼文月曆.xlsx
+++ b/十全特好_7-9月FB貼文月曆.xlsx
@@ -36,7 +36,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="006A1B9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,45 +115,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -513,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -524,9 +540,11 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -585,37 +603,47 @@
           <t>追蹤指標</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>配圖方向（Olivia）</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>重點元素</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="120" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>2025/7/1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>抽獎倒數 2 週，加入會員還來得及</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>6/15 開始的抽獎活動，7/15 第一次開抽。
 現在還有兩週，還沒加入官網會員的，
@@ -626,57 +654,67 @@
 👉 加入連結在留言區</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>#十全特好 #會員限定 #抽獎活動</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>獎品實物 + 倒數「14 天」字樣</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>朱紅底，白字「倒數 14 天」佔畫面 50%，獎品實物放右側</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>大數字、獎品照</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2025/7/4</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>夏天一鍋涼拌，米醋是關鍵</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>米醋</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>不開火也能吃得很好。
 小黃瓜拍碎，加蒜末、辣椒、一匙米醋、少許鹽。
@@ -686,57 +724,67 @@
 這道夏天每週至少做兩次，你試試。</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>#夏日食譜 #涼拌 #十全米醋</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>成品俯拍，自然光，不要太精緻感</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>小黃瓜涼拌俯拍，自然光，米白碗，木桌背景，左上角小字「5 分鐘料理」</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>清爽感、夏天色調</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>2025/7/8</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>你家的烏醋是釀的還是調的？</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>烏醋</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>翻一下你家烏醋的成分表。
 第幾行出現「焦糖色素」？
@@ -746,57 +794,67 @@
 不是每瓶烏醋都一樣，只是大部分人沒有翻過成分表。</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>#成分控 #天然釀造 #十全烏醋</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>兩瓶烏醋成分表並排對比，文字清晰可讀</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>兩瓶醋並排，成分表各自清楚可讀，深青綠底條做區隔</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>對比感強、文字清晰</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>2025/7/11</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>7/15 開抽，倒數 4 天</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>7/15 開抽，倒數 4 天。
 這次抽 300 名，名額比你想的多，
@@ -807,57 +865,67 @@
 👉 加入連結在留言區</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>#十全特好 #倒數 #抽獎最後機會</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>「倒數 4 天」大字設計，搭配獎品圖</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>朱紅底，「倒數 4 天」極大白字，下方一行小字說明資格</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>緊迫感、數字要大</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2025/7/15</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>第一次抽獎得獎公告，300 名出爐</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>第一批 300 位，出爐了。
 感謝這個月加入的每一位新會員，
@@ -868,57 +936,67 @@
 得獎名單查詢：[連結]</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎結果 #恭喜得獎</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>「恭喜 300 位得獎」簡潔圖卡，品牌色系</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>深醬色底，「恭喜 300 位」金色字，溫暖收穫感</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>慶祝感、金色點綴</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>2025/7/18</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>味噌湯不只一種喝法，三個懶人版本</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>味噌</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>味噌湯不只一種喝法。
 最懶版：味噌 + 豆腐 + 蔥花，三分鐘。
@@ -930,57 +1008,67 @@
 比想像中好喝，你試試。</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>#味噌湯 #日式料理 #十全味噌</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>三種版本的味噌湯並排，或選最好看的一道主拍</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>三碗味噌湯並排俯拍，分別標「3 分鐘」「進階版」「冷湯」</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>清晰對比、三等分構圖</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2025/7/22</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>味醂不是米酒，差在哪裡</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>味醂</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>很多人把味醂當米酒用，錯了。
 米酒：去腥，讓肉軟一點。
@@ -991,57 +1079,67 @@
 看看顏色和味道差在哪。</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>#料理知識 #味醂 #十全味醂</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>照燒肉特寫，油亮光澤感明顯</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>照燒豬肉特寫，油亮光澤，右側文字框說明味醂功效</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>食材光澤、文字輔助</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>2025/7/25</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>8 月抽獎預告，資格自動保留到 9 月</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>7 月抽完了，8 月繼續。
 8/15 第二次抽獎，還是 300 名，
@@ -1053,57 +1151,67 @@
 還沒加入的，現在是第二次機會。</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎活動 #會員限定</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>三個月抽獎時間軸圖卡（7/15 ✓、8/15、9/15）</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>連結點擊數、分享數</t>
         </is>
       </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>三格時間軸圖卡（7/15 ✓ 綠勾、8/15 圓圈、9/15 圓圈），朱紅強調下兩場</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>進度感、視覺清楚</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>2025/8/1</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>中元普渡三道家常菜，食材不浪費</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>味噌、烏醋、辣椒醬</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>中元普渡快到了，拜拜完的食材怎麼辦？
 三道不浪費的家常菜：
@@ -1116,57 +1224,67 @@
 拜完直接煮，不用另外買食材。</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>#中元節 #普渡料理 #十全調味</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>三道菜並排，家常感，不要太精緻</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>三道菜三格構圖，每格一道，左上角各標菜名，家常實物感</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>三等分、豐盛感</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>2025/8/5</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>中元禮盒開賣，會員早鳥優惠</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>禮盒</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>中元節送禮，送什麼不失禮？
 健康調味禮盒，對象是全家都能用的：
@@ -1178,57 +1296,67 @@
 👉 禮盒詳情在留言區</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>#中元送禮 #十全特好 #健康禮盒</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>禮盒實物正面，質感包裝，乾淨背景</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>連結點擊數、私訊數</t>
         </is>
       </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>禮盒正面大圖，乾淨白底，右側文字「會員早鳥」紅色標籤</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>產品主角、標籤搶眼</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>2025/8/8</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>辣椒醬成分表，你上次看是什麼時候</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>辣椒醬</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>辣椒醬的成分表，你上次看是什麼時候？
 常見的：辣椒、大豆油、防腐劑、調味劑、色素。
@@ -1240,57 +1368,67 @@
 很少回頭買合成的。</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>#成分控 #辣椒醬 #十全辣椒醬</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>成分表對比圖，文字要夠大夠清楚</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr">
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>辣椒醬瓶身 + 成分表放大，兩欄對比，左合成右天然</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>對比版面、文字大</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>2025/8/12</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天。
 7 月已經抽了 300 名，
@@ -1302,57 +1440,67 @@
 👉 官網加入連結在留言區</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎倒數 #會員限定</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>「倒數 3 天」+ 累計已抽 300 名圖卡</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr">
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>朱紅底，「倒數 3 天」白字大，下方進度條「600/900」</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>緊迫感、累積進度</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>2025/8/15</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>第二次抽獎公告，累計 600 名得獎</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>第二批 300 位，出爐了。
 兩個月，累計 600 位得獎會員。
@@ -1363,57 +1511,67 @@
 得獎名單查詢：[連結]</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎結果 #恭喜得獎</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>「累計 600 位得獎」圖卡，有進度感</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>深醬色底，「累計 600 位得獎」金字，中間進度條已填 2/3</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>進度感、溫暖</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>2025/8/19</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>辣椒醬不只沾著吃，三種懶人料理</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>辣椒醬</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>辣椒醬不只是沾醬。
 三種懶人用法：
@@ -1429,57 +1587,67 @@
 一瓶用三種方式，物超所值。</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>#辣椒醬料理 #懶人食譜 #十全辣椒醬</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>三種料理並排，或選最好看的一道主拍</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>三種料理橫排或三格，蛤蜊/拌麵/烤雞各一，自然光</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>豐富感、料理質感</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>2025/8/22</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>釀造醋 vs 調製醋，成分表不會說謊</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>烏醋、米醋</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>買醋之前，先翻成分表。
 調製醋：水、醋酸、焦糖色素、調味劑。
@@ -1490,57 +1658,67 @@
 是叫你養成翻成分表的習慣。</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>#成分控 #釀造醋 #十全烏醋</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>兩種成分表並排對比，文字清晰可讀</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K16" s="10" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>成分表兩欄並排，左側打 ✗，右側打 ✓，深青綠底強調</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>對比清晰、判斷感</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>2025/8/26</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>9/15 最終場預告 + 中秋禮盒預熱</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>全系列、禮盒</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>9/15 是最後一次，第三次抽獎。
 三個月抽了 600 名，
@@ -1552,57 +1730,67 @@
 詳情下週公布，先追蹤不要錯過。</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>#十全特好 #中秋禮盒 #抽獎最終場</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>一半中秋氛圍、一半抽獎倒數，雙主題圖卡</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr">
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>追蹤數、分享數</t>
         </is>
       </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>上半中秋月亮氛圍，下半「最終場 9/15」倒數，分割構圖</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>雙主題、視覺切割</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>2025/9/2</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>中秋禮盒正式開賣，會員優先購</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>禮盒</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>中秋送禮，今年換個思路。
 月餅吃完就忘，
@@ -1615,57 +1803,67 @@
 👉 禮盒詳情在留言區</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>#中秋送禮 #十全特好 #天然調味禮盒</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>禮盒與中秋氛圍結合，質感攝影</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>連結點擊數、私訊數</t>
         </is>
       </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>禮盒 + 月亮背景，深夜質感，右側「會員優先購」標籤</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>中秋氛圍、禮品感</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>2025/9/5</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>中秋烤肉醬自己調，烏醋 + 辣椒醬</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>烏醋、辣椒醬</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>中秋烤肉，醬料自己調的和買的，差一個層次。
 基底烤肉醬配方：
@@ -1677,57 +1875,67 @@
 比瓶裝烤肉醬好吃，成本少很多。</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>#中秋烤肉 #烤肉醬 #十全調味</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>烤肉實境，搭配醬料小碗，煙霧感</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>烤肉現場俯拍，炭火煙霧感，小碗自調醬料放前景</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>煙霧感、生活感強</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>2025/9/9</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>最終場抽獎倒數 6 天，這次沒加入就真的沒了</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>9/15，最後一次。
 三個月，共三次抽獎，每次 300 名。
@@ -1741,57 +1949,67 @@
 👉 加入連結在留言區</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎最終場 #倒數</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>「最終場 倒數 6 天」大字圖卡，有緊迫感</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>朱紅底，「最終場 倒數 6 天」白字極大，緊張感拉滿</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>最大衝擊感</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>2025/9/12</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>好的味噌，需要時間</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>味噌</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>好的味噌，需要時間。
 黃豆、米麴、鹽，
@@ -1804,57 +2022,67 @@
 你的舌頭會告訴你差在哪。</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>#味噌 #發酵食品 #十全味噌</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>釀造過程質感照，或木桶、黃豆等原料特寫</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>木桶或陶甕，靜物感，柔和打光，日系工藝質感</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>時間感、工藝感</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>2025/9/15</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>最終場抽獎公告，累計 900 名得獎，感謝支持</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>最後一批，300 位，出爐了。
 三個月，三次抽獎，
@@ -1867,57 +2095,67 @@
 下一個活動，等我們。</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎結果 #感謝支持</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>「累計 900 位得獎，感謝支持」溫暖收尾圖卡</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="K22" s="15" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>深醬色底，「累計 900 位，謝謝你們」金字，溫暖收尾</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>感謝感、完結感</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="120" customHeight="1">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>2025/9/19</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>秋天一鍋味噌豬肉湯，周末煮一次</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>味噌</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>天氣一涼，就想煮這鍋。
 味噌豬肉湯，周末煮一次，
@@ -1932,57 +2170,67 @@
 你會一直煮。</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>#秋天食譜 #味噌豬肉湯 #十全味噌</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>熱湯冒煙的溫暖感，秋天色調</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>味噌豬肉湯，蒸氣冒煙，秋天橘調光線，木碗或陶碗</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>暖色、食慾感</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="120" customHeight="1">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>2025/9/23</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>中秋禮盒最後機會 + 雙十會員搶先看預告</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>禮盒、全系列</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>中秋禮盒，最後幾天。
 還沒送的，今天訂，還來得及。
@@ -1994,57 +2242,67 @@
 👉 中秋禮盒連結在留言區</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>#中秋禮盒 #十全特好 #雙十預告</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>中秋收尾 + 雙十倒數感，兩個訊息並陳</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K24" s="15" t="inlineStr">
         <is>
           <t>連結點擊數、追蹤數</t>
         </is>
       </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>左禮盒、右「雙十預告」箭頭指向，分割畫面設計</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>兩個訊息並陳</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="120" customHeight="1">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>2025/9/26</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>天然調味料怎麼挑？看這三個字就夠了</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>天然調味料怎麼挑？
 看這三個字就夠了。
@@ -2058,24 +2316,34 @@
 「釀造」兩個字在不在，答案就出來了。</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H25" s="15" t="inlineStr">
         <is>
           <t>#天然調味 #釀造 #十全特好</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>成分表特寫，「釀造」兩個字清楚圈出</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K25" s="15" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>成分表特寫，紅圈圈出「釀造」兩字，深青綠底色</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>聚焦細節、強調字</t>
         </is>
       </c>
     </row>
@@ -2090,15 +2358,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>顏色</t>
         </is>
@@ -2110,7 +2378,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>藍色底</t>
         </is>
@@ -2122,7 +2390,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>綠色底</t>
         </is>
@@ -2134,7 +2402,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>黃色底</t>
         </is>
@@ -2146,7 +2414,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>紅色類型</t>
         </is>
@@ -2158,7 +2426,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>橘色類型</t>
         </is>
@@ -2170,14 +2438,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>紫色類型</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>粉紫色類型</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>知識類貼文</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>淺紫色欄</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Olivia 配圖方向（第 12-13 欄）</t>
         </is>
       </c>
     </row>
